--- a/sheets/대금율보/검수/배띄워라.xlsx
+++ b/sheets/대금율보/검수/배띄워라.xlsx
@@ -6115,7 +6115,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
@@ -6309,7 +6309,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 㴌</t>
         </is>
       </c>
@@ -6331,7 +6331,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -6342,7 +6342,7 @@
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰‹</t>
+汰</t>
         </is>
       </c>
       <c r="I5" s="23" t="inlineStr">
@@ -6353,7 +6353,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-㴌‹</t>
+㴌</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
@@ -6364,7 +6364,7 @@
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-㴌‹</t>
+㴌</t>
         </is>
       </c>
       <c r="M5" s="23" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="Q5" s="23" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="R5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 㴌</t>
         </is>
       </c>
@@ -6519,7 +6519,7 @@
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南‹
+          <t xml:space="preserve">南
 –潢</t>
         </is>
       </c>
@@ -6563,7 +6563,7 @@
       <c r="C8" s="23"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌‹
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -6603,7 +6603,7 @@
       <c r="M8" s="23"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –潢</t>
         </is>
       </c>
@@ -6649,13 +6649,13 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="G9" s="23"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –南</t>
         </is>
       </c>
@@ -6678,7 +6678,7 @@
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-㴌‹</t>
+㴌</t>
         </is>
       </c>
       <c r="M9" s="23"/>
@@ -6687,13 +6687,13 @@
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="Q9" s="23"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
@@ -6789,7 +6789,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹
+          <t xml:space="preserve">林
 –南</t>
         </is>
       </c>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –湳</t>
         </is>
       </c>
@@ -6924,14 +6924,14 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰‹</t>
+汰</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -6983,7 +6983,7 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-㴌‹</t>
+㴌</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 㴌</t>
         </is>
       </c>
@@ -7009,7 +7009,7 @@
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="O13" s="23" t="inlineStr">
@@ -7020,7 +7020,7 @@
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-㴌‹</t>
+㴌</t>
         </is>
       </c>
       <c r="Q13" s="23" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –湳</t>
         </is>
       </c>
@@ -7153,7 +7153,7 @@
       <c r="Q15" s="22"/>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
@@ -7210,7 +7210,7 @@
       <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="K16" s="23"/>
@@ -7239,7 +7239,7 @@
       <c r="Q16" s="23"/>
       <c r="R16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
@@ -7272,7 +7272,7 @@
       <c r="E17" s="23"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌‹
+          <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
@@ -7293,7 +7293,7 @@
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-汰‹</t>
+汰</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -7304,14 +7304,14 @@
       <c r="N17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-㴌‹</t>
+㴌</t>
         </is>
       </c>
       <c r="Q17" s="23"/>
@@ -7524,7 +7524,7 @@
       <c r="T23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="U23" s="23" t="inlineStr">
@@ -7737,7 +7737,7 @@
       <c r="T31" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-湳‹</t>
+湳</t>
         </is>
       </c>
       <c r="U31" s="23" t="inlineStr">

--- a/sheets/대금율보/검수/배띄워라.xlsx
+++ b/sheets/대금율보/검수/배띄워라.xlsx
@@ -6059,32 +6059,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7409,10 +7409,10 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="6.0" customHeight="true">
       <c r="A19" s="0"/>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="80.0" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="20" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="89.42" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="22"/>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="89.42" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="23"/>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="89.42" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="23"/>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="89.42" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="24"/>
@@ -7556,7 +7556,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="24"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="89.42" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -7579,7 +7579,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="89.42" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="23"/>
@@ -7602,7 +7602,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="89.42" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -7625,7 +7625,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="89.42" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="U28" s="24"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="89.42" customHeight="true">
       <c r="A29" s="0"/>
       <c r="B29" s="21"/>
       <c r="C29" s="22"/>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="89.42" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="21"/>
       <c r="C30" s="23"/>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="89.42" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="23"/>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="89.42" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="24"/>
@@ -7769,7 +7769,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="24"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="89.42" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="22"/>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="89.42" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="23"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="U34" s="23"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="89.42" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="23"/>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="89.42" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="24"/>
@@ -7885,7 +7885,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="18" max="16383" man="1"/>
   </rowBreaks>
